--- a/MinMax/scripts/comparison/violations_comparison_table_118_2.xlsx
+++ b/MinMax/scripts/comparison/violations_comparison_table_118_2.xlsx
@@ -459,16 +459,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.0002233475970569998</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0001399708271492273</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0.0094401640817523</v>
+        <v>0.009438122622668743</v>
       </c>
       <c r="E2">
-        <v>0.01072692219167948</v>
+        <v>0.01072486769407988</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -476,10 +476,10 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.009590625762939453</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.009832859039306641</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0.1031439304351807</v>
@@ -493,16 +493,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.0004305202164687216</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.0001864765217760578</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0.006919256877154112</v>
+        <v>0.006921404972672462</v>
       </c>
       <c r="E4">
-        <v>0.006358384154736996</v>
+        <v>0.006360669154673815</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -510,16 +510,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.02275671251118183</v>
+        <v>-0</v>
       </c>
       <c r="C5">
-        <v>0.009074035100638866</v>
+        <v>-0</v>
       </c>
       <c r="D5">
-        <v>0.07458078861236572</v>
+        <v>0.07480859756469727</v>
       </c>
       <c r="E5">
-        <v>0.09197914600372314</v>
+        <v>0.09221112728118896</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -629,10 +629,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.0001612487540114671</v>
+        <v>0.0001612538035260513</v>
       </c>
       <c r="C12">
-        <v>0.0001612681953702122</v>
+        <v>0.0001612729975022376</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.01907432079315186</v>
+        <v>0.01907521486282349</v>
       </c>
       <c r="C13">
         <v>0.01907849311828613</v>
@@ -663,10 +663,10 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.1712267994880676</v>
+        <v>0.1712257862091064</v>
       </c>
       <c r="C14">
-        <v>0.1712238639593124</v>
+        <v>0.1712239980697632</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>8.213314056396484</v>
+        <v>8.213106155395508</v>
       </c>
       <c r="C15">
-        <v>8.213388442993164</v>
+        <v>8.213287353515625</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -697,16 +697,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>4.866746939658408E-08</v>
+        <v>5.748119373000132E-08</v>
       </c>
       <c r="C16">
-        <v>6.859102191044069E-08</v>
+        <v>5.004381185351881E-08</v>
       </c>
       <c r="D16">
-        <v>2.641873172277392E-06</v>
+        <v>2.57224269262224E-06</v>
       </c>
       <c r="E16">
-        <v>2.646063509217875E-06</v>
+        <v>2.545463985370588E-06</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -714,16 +714,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>4.488684835498315E-07</v>
+        <v>1.635749677716623E-06</v>
       </c>
       <c r="C17">
-        <v>2.925459086371652E-06</v>
+        <v>4.156315853312338E-07</v>
       </c>
       <c r="D17">
-        <v>3.170147799968417E-05</v>
+        <v>2.23520601139171E-05</v>
       </c>
       <c r="E17">
-        <v>1.856029354519867E-05</v>
+        <v>1.85602930287132E-05</v>
       </c>
     </row>
   </sheetData>
